--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44410</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44410</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44410</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44410</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>44410</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44410</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44410</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44410</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44410</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44410</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44410</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44410</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44419</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44421</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44427</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44432</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44433</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44438</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44447</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44452</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44452</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44453</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44455</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>44456</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44456</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44460</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44462</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44464</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44464</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44463</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44467</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44469</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44470</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44473</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44473</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44476</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44476</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44480</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>44481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44483</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>44488</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44488</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44489</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44495</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>44496</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44502</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>44503</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44504</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44511</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44515</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44515</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>44529</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44533</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44533</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>44543</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44543</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>44550</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44550</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44550</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44550</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44560</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44566</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>44574</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44580</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44581</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44587</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44588</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44594</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44596</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44599</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44599</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44600</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44606</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>44606</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44606</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44606</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44606</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44606</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44606</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44606</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>44609</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>44610</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44610</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>44619</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44619</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44620</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44628</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44631</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44642</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44653</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44653</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>44670</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44672</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44679</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>44679</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44687</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44701</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44706</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>44714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>44715</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44715</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44727</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44729</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44729</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44729</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44731</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44734</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44740</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44740</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44740</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44742</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44742</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44750</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44756</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44772</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44772</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44774</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44774</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>44774</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44777</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44781</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44784</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44784</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44785</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>44788</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44790</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44792</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44797</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44798</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44802</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>44802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>44804</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44805</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44805</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44810</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44811</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44813</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>44813</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44813</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>44816</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>44816</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44816</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44817</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44818</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>44818</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44820</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44824</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>44825</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>44825</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>44830</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>44830</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44830</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44838</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44838</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>44838</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>44838</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>44839</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44839</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44839</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>44840</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>44840</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>44840</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>44841</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44841</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44840</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44841</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>44841</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44841</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44841</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44844</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>44846</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44846</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44846</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44846</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>44846</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44846</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44847</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44847</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44848</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44848</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44851</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44853</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44855</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44858</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44859</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44859</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>44859</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44859</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44860</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>44861</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44861</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44861</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>44862</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44865</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44865</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44865</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44867</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44872</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>44872</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44873</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44873</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44873</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44874</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>44874</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>44874</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>44874</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44876</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44876</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44876</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44876</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44896</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44896</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44896</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44900</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44900</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44900</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>44900</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44902</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44902</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44904</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44908</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>44914</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>44914</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>44914</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44917</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>44920</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44929</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44929</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44931</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44931</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44937</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44939</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44944</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44944</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>44944</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44944</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44944</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44944</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44949</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44953</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44957</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44958</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>44958</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44967</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>44972</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44977</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44980</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44980</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44981</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44981</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44983</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>44984</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44987</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44988</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45006</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45007</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45007</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45009</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45012</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45013</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45014</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45015</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45016</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45016</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45016</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45016</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45016</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45016</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45017</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45019</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45022</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45028</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45029</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45030</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45033</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45034</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45033</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45034</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45034</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45034</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45040</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45041</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45041</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45041</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45041</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45042</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45043</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45043</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45043</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45047</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45048</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45048</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45055</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45056</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45056</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45058</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45065</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45065</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45069</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45068</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45070</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45070</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45071</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45071</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45076</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45077</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45077</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45077</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45078</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45078</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45078</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45082</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45084</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45084</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45085</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45086</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45086</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45088</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45089</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45089</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45089</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45091</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45091</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45091</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45091</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45091</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45096</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45096</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45096</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45096</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45096</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45098</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45099</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45099</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45099</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45099</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45103</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45105</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45106</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45106</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45107</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45107</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45110</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45110</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45110</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45111</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45112</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45113</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45114</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45114</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45116</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45121</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45121</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45121</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45121</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45128</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45138</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45140</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45140</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45140</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45141</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45142</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45145</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45154</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45160</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45160</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45160</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45163</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45165</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45166</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45166</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45166</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45166</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45167</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45167</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45167</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45167</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45167</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45167</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45167</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45167</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45168</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45168</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45173</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45173</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45173</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45173</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45173</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45174</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45174</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45175</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45176</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45176</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45177</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45180</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45181</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45182</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45183</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45183</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45188</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45188</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45189</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45189</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45191</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45194</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45197</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45197</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45197</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45198</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45198</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45198</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45198</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45199</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45202</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45202</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45202</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45202</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45202</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45202</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45204</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45204</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>45205</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45208</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45208</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45209</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45209</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45210</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45211</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45211</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45211</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45215</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45215</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45215</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45215</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45215</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45215</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45215</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45215</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45216</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45216</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45216</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45216</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>45216</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45216</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
         <v>45216</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45216</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45216</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45217</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45217</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45217</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>45217</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>45222</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45225</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>45226</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45230</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45230</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45236</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45238</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64022,14 +64022,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 55909-2023</t>
+          <t>A 55790-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64042,7 +64042,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -64086,7 +64086,7 @@
         <v>45239</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64136,14 +64136,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 55790-2023</t>
+          <t>A 55909-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64156,7 +64156,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64200,7 +64200,7 @@
         <v>45242</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45243</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>45244</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45244</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>45247</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>45249</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64542,7 +64542,7 @@
         <v>45250</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64599,7 +64599,7 @@
         <v>45250</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64656,7 +64656,7 @@
         <v>45250</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64706,14 +64706,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 59157-2023</t>
+          <t>A 59152-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64763,14 +64763,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 59152-2023</t>
+          <t>A 59157-2023</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -64820,14 +64820,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 59289-2023</t>
+          <t>A 59228-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -64877,14 +64877,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 59228-2023</t>
+          <t>A 59220-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -64934,14 +64934,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 59220-2023</t>
+          <t>A 59333-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -64991,14 +64991,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 59333-2023</t>
+          <t>A 59289-2023</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -65011,7 +65011,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -65055,7 +65055,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45257</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -65169,7 +65169,7 @@
         <v>45257</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45258</v>
+        <v>45259</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44410</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44410</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44410</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44410</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>44410</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44410</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44410</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44410</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44410</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44410</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44410</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44410</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44419</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44421</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44427</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44432</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44433</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44438</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44447</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44452</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44452</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44453</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44455</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>44456</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44456</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44460</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44462</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44464</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44464</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44463</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44467</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44469</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44470</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44473</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44473</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44476</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44476</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44480</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>44481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44483</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>44488</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44488</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44489</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44495</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>44496</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44502</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>44503</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44504</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44511</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44515</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44515</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>44529</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44533</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44533</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>44543</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44543</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>44550</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44550</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44550</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44550</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44560</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44566</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>44574</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44580</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44581</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44587</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44588</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44594</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44596</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44599</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44599</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44600</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44606</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>44606</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44606</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44606</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44606</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44606</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44606</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44606</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>44609</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>44610</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44610</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>44619</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44619</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44620</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44628</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44631</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44642</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44653</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44653</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>44670</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44672</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44679</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>44679</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44687</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44701</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44706</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>44714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>44715</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44715</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44727</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44729</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44729</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44729</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44731</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44734</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44740</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44740</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44740</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44742</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44742</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44750</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44756</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44772</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44772</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44774</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44774</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>44774</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44777</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44781</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44784</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44784</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44785</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>44788</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44790</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44792</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44797</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44798</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44802</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>44802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>44804</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44805</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44805</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44810</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44811</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44813</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>44813</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44813</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>44816</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>44816</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44816</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44817</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44818</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>44818</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44820</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44824</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>44825</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>44825</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>44830</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>44830</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44830</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44838</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44838</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>44838</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>44838</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>44839</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44839</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44839</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>44840</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>44840</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>44840</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>44841</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44841</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44840</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44841</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>44841</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44841</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44841</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44844</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>44846</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44846</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44846</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44846</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>44846</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44846</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44847</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44847</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44848</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44848</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44851</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44853</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44855</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44858</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44859</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44859</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>44859</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44859</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44860</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>44861</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44861</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44861</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>44862</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44865</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44865</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44865</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44867</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44872</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>44872</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44873</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44873</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44873</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44874</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>44874</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>44874</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>44874</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44876</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44876</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44876</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44876</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44896</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44896</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44896</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44900</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44900</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44900</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>44900</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44902</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44902</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44904</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44908</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>44914</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>44914</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>44914</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44917</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>44920</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44929</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44929</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44931</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44931</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44937</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44939</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44944</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44944</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>44944</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44944</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44944</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44944</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44949</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44953</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44957</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44958</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>44958</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44967</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>44972</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44977</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44980</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44980</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44981</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44981</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44983</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>44984</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44987</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44988</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45006</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45007</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45007</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45009</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45012</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45013</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45014</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45015</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45016</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45016</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45016</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45016</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45016</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45016</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45017</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45019</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45022</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45028</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45029</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45030</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45033</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45034</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45033</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45034</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45034</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45034</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45040</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45041</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45041</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45041</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45041</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45042</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45043</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45043</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45043</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45047</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45048</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45048</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45055</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45056</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45056</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45058</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45065</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45065</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45069</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45068</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45070</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45070</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45071</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45071</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45076</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45077</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45077</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45077</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45078</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45078</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45078</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45082</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45084</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45084</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45085</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45086</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45086</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45088</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45089</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45089</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45089</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45091</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45091</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45091</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45091</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45091</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45096</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45096</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45096</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45096</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45096</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45098</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45099</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45099</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45099</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45099</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45103</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45105</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45106</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45106</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45107</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45107</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45110</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45110</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45110</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45111</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45112</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45113</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45114</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45114</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45116</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45121</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45121</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45121</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45121</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45128</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45138</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45140</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45140</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45140</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45141</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45142</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45145</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45154</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45160</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45160</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45160</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45163</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45165</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45166</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45166</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45166</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45166</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45167</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45167</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45167</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45167</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45167</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45167</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45167</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45167</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45168</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45168</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45173</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45173</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45173</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45173</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45173</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45174</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45174</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45175</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45176</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45176</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45177</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45180</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45181</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45182</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45183</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45183</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45188</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45188</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45189</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45189</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45191</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45194</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45197</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45197</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45197</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45198</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45198</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45198</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45198</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45199</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45202</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45202</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45202</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45202</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45202</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45202</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45204</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45204</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>45205</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45208</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45208</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45209</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45209</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45210</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45211</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45211</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45211</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45215</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45215</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45215</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45215</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45215</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45215</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45215</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45215</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45216</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45216</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45216</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45216</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>45216</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45216</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
         <v>45216</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45216</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45216</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45217</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45217</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45217</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>45217</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>45222</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45225</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>45226</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45230</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45230</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45236</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45238</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64022,14 +64022,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 55790-2023</t>
+          <t>A 55911-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64042,7 +64042,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -64079,14 +64079,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 55911-2023</t>
+          <t>A 55909-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64099,7 +64099,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -64136,14 +64136,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 55909-2023</t>
+          <t>A 55790-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64156,7 +64156,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64200,7 +64200,7 @@
         <v>45242</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45243</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>45244</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45244</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>45247</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>45249</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64542,7 +64542,7 @@
         <v>45250</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64599,7 +64599,7 @@
         <v>45250</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64656,7 +64656,7 @@
         <v>45250</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64706,14 +64706,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 59152-2023</t>
+          <t>A 59157-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64763,14 +64763,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 59157-2023</t>
+          <t>A 59152-2023</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -64820,14 +64820,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 59228-2023</t>
+          <t>A 59220-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -64877,14 +64877,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 59220-2023</t>
+          <t>A 59333-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -64934,14 +64934,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 59333-2023</t>
+          <t>A 59228-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -64998,7 +64998,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -65055,7 +65055,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45257</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -65169,7 +65169,7 @@
         <v>45257</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1060"/>
+  <dimension ref="A1:Y1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44410</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44410</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44410</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44410</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>44410</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44410</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44410</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44410</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44410</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44410</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44410</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44410</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44419</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44421</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44427</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44432</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44433</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44438</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44447</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44452</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44452</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44453</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44455</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>44456</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44456</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44460</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44462</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44464</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44464</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44463</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44467</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44469</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44470</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44473</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44473</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44476</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44476</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44480</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>44481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44483</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>44488</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44488</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44489</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44495</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>44496</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44502</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>44503</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44504</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44511</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44515</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44515</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>44529</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44533</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44533</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>44543</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44543</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>44550</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44550</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44550</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44550</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44560</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44566</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>44574</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44580</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44581</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44587</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44588</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44594</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44596</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44599</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44599</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44600</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44606</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>44606</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44606</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44606</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44606</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44606</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44606</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44606</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>44609</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>44610</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44610</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>44619</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44619</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44620</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44628</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44631</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44642</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44653</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44653</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>44670</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44672</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44679</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>44679</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44687</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44701</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44706</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>44714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>44715</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44715</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44727</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44729</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44729</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44729</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44731</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44734</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44740</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44740</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44740</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44742</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44742</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44750</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44756</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44772</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44772</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44774</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44774</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>44774</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44777</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44781</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44784</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44784</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44785</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>44788</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44790</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44792</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44797</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44798</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44802</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>44802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>44804</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44805</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44805</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44810</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44811</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44813</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>44813</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44813</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>44816</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>44816</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44816</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44817</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44818</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>44818</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44820</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44824</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>44825</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>44825</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>44830</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>44830</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44830</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44838</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44838</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>44838</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>44838</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>44839</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44839</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44839</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>44840</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>44840</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>44840</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>44841</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44841</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44840</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44841</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>44841</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44841</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44841</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44844</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>44846</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44846</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44846</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44846</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>44846</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44846</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44847</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44847</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44848</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44848</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44851</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44853</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44855</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44858</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44859</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44859</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>44859</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44859</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44860</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>44861</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44861</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44861</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>44862</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44865</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44865</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44865</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44867</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44872</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>44872</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44873</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44873</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44873</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44874</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>44874</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>44874</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>44874</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44876</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44876</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44876</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44876</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44896</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44896</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44896</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44900</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44900</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44900</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>44900</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44902</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44902</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44904</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44908</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>44914</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>44914</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>44914</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44917</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>44920</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44929</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44929</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44931</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44931</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44937</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44939</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44944</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44944</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>44944</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44944</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44944</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44944</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44949</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44953</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44957</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44958</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>44958</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44967</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>44972</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44977</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44980</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44980</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44981</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44981</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44983</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>44984</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44987</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44988</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45006</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45007</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45007</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45009</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45012</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45013</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45014</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45015</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45016</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45016</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45016</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45016</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45016</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45016</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45017</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45019</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45022</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45028</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45029</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45030</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45033</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45034</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45033</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45034</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45034</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45034</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45040</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45041</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45041</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45041</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45041</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45042</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45043</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45043</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45043</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45047</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45048</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45048</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45055</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45056</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45056</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45058</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45065</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45065</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45069</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45068</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45070</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45070</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45071</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45071</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45076</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45077</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45077</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45077</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45078</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45078</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45078</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45082</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45084</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45084</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45085</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45086</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45086</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45088</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45089</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45089</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45089</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45091</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45091</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45091</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45091</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45091</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45096</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45096</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45096</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45096</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45096</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45098</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45099</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45099</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45099</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45099</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45103</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45105</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45106</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45106</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45107</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45107</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45110</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45110</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45110</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45111</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45112</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45113</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45114</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45114</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45116</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45121</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45121</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45121</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45121</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45128</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45138</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45140</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45140</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45140</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45141</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45142</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45145</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45154</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45160</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45160</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45160</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45163</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45165</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45166</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45166</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45166</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45166</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45167</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45167</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45167</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45167</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45167</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45167</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45167</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45167</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45168</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45168</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45173</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45173</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45173</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45173</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45173</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45174</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45174</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45175</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45176</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45176</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45177</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45180</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45181</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45182</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45183</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45183</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45188</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45188</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45189</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45189</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45191</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45194</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45197</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45197</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45197</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45198</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45198</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45198</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45198</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45199</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45202</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45202</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45202</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45202</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45202</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45202</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45204</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45204</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>45205</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45208</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45208</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45209</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45209</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45210</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45211</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45211</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45211</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45215</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45215</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45215</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45215</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45215</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45215</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45215</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45215</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45216</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45216</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45216</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45216</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>45216</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45216</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
         <v>45216</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45216</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45216</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45217</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45217</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45217</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>45217</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>45222</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45225</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>45226</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45230</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45230</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45236</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45238</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64022,14 +64022,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 55911-2023</t>
+          <t>A 55909-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64042,7 +64042,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -64079,14 +64079,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 55909-2023</t>
+          <t>A 55790-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64099,7 +64099,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -64136,14 +64136,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 55790-2023</t>
+          <t>A 55911-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64156,7 +64156,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64200,7 +64200,7 @@
         <v>45242</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45243</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>45244</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45244</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>45247</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>45249</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64535,14 +64535,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 58256-2023</t>
+          <t>A 58245-2023</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>0.3</v>
+        <v>8.5</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -64592,14 +64592,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 58245-2023</t>
+          <t>A 58262-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64649,14 +64649,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 58262-2023</t>
+          <t>A 58256-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64669,7 +64669,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64713,7 +64713,7 @@
         <v>45251</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45251</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64827,7 +64827,7 @@
         <v>45252</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64884,7 +64884,7 @@
         <v>45252</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -64934,14 +64934,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 59228-2023</t>
+          <t>A 59289-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -64991,14 +64991,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 59289-2023</t>
+          <t>A 59228-2023</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -65011,7 +65011,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -65055,7 +65055,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45257</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
       </c>
       <c r="R1059" s="2" t="inlineStr"/>
     </row>
-    <row r="1060">
+    <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
           <t>A 59963-2023</t>
@@ -65169,7 +65169,7 @@
         <v>45257</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -65215,6 +65215,63 @@
         <v>0</v>
       </c>
       <c r="R1060" s="2" t="inlineStr"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>A 60645-2023</t>
+        </is>
+      </c>
+      <c r="B1061" s="1" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C1061" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>UMEÅ</t>
+        </is>
+      </c>
+      <c r="G1061" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1061" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1061"/>
+  <dimension ref="A1:Y1064"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44410</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44410</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44410</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44410</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>44410</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44410</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44410</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44410</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44410</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44410</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44410</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44410</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44419</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44421</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44427</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44432</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44433</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44438</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44447</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44452</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44452</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44453</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44455</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>44456</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44456</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44460</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44462</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44464</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44464</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44463</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44467</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44469</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44470</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44473</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44473</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44476</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44476</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44480</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>44481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44483</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>44488</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44488</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44489</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44495</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>44496</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44502</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>44503</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44504</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44511</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44515</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44515</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>44529</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44533</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44533</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>44543</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44543</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>44550</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44550</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44550</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44550</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44560</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44566</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>44574</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44580</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44581</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44587</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44588</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44594</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44596</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44599</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44599</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44600</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44606</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>44606</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44606</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44606</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44606</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44606</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44606</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44606</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>44609</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>44610</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44610</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>44619</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44619</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44620</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44628</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44631</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44642</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44653</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44653</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>44670</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44672</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44679</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>44679</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44687</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44701</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44706</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>44714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>44715</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44715</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44727</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44729</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44729</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44729</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44731</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44734</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44740</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44740</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44740</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44742</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44742</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44750</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44756</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44772</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44772</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44774</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44774</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>44774</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44777</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44781</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44784</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44784</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44785</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>44788</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44790</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44792</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44797</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44798</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44802</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>44802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>44804</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44805</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44805</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44810</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44811</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44813</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>44813</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44813</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>44816</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>44816</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44816</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44817</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44818</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>44818</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44820</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44824</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>44825</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>44825</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>44830</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>44830</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44830</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44838</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44838</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>44838</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>44838</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>44839</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44839</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44839</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>44840</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>44840</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>44840</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>44841</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44841</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44840</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44841</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>44841</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44841</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44841</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44844</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>44846</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44846</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44846</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44846</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>44846</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44846</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44847</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44847</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44848</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44848</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44851</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44853</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44855</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44858</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44859</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44859</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>44859</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44859</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44860</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>44861</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44861</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44861</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>44862</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44865</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44865</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44865</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44867</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44872</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>44872</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44873</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44873</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44873</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44874</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>44874</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>44874</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>44874</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44876</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44876</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44876</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44876</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44896</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44896</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44896</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44900</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44900</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44900</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>44900</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44902</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44902</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44904</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44908</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>44914</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>44914</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>44914</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44917</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>44920</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44929</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44929</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44931</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44931</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44937</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44939</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44944</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44944</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>44944</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44944</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44944</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44944</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44949</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44953</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44957</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44958</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>44958</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44967</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>44972</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44977</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44980</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44980</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44981</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44981</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44983</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>44984</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44987</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44988</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45006</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45007</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45007</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45009</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45012</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45013</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45014</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45015</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45016</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45016</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45016</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45016</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45016</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45016</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45017</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45019</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45022</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45028</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45029</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45030</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45033</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45034</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45033</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45034</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45034</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45034</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45040</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45041</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45041</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45041</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45041</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45042</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45043</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45043</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45043</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45047</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45048</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45048</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45055</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45056</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45056</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45058</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45065</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45065</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45069</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45068</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45070</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45070</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45071</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45071</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45076</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45077</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45077</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45077</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45078</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45078</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45078</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45082</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45084</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45084</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45085</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45086</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45086</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45088</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45089</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45089</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45089</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45091</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45091</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45091</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45091</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45091</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45096</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45096</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45096</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45096</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45096</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45098</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45099</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45099</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45099</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45099</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45103</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45105</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45106</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45106</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45107</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45107</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45110</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45110</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45110</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45111</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45112</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45113</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45114</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45114</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45116</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45121</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45121</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45121</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45121</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45128</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45138</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45140</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45140</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45140</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45141</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45142</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45145</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45154</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45160</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45160</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45160</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45163</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45165</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45166</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45166</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45166</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45166</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45167</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45167</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45167</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45167</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45167</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45167</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45167</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45167</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45168</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45168</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45173</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45173</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45173</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45173</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45173</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45174</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45174</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45175</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45176</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45176</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45177</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45180</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45181</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45182</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45183</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45183</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45188</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45188</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45189</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45189</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45191</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45194</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45197</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45197</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45197</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45198</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45198</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45198</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45198</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45199</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45202</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45202</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45202</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45202</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45202</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45202</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45204</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45204</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>45205</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45208</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45208</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45209</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45209</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45210</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45211</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45211</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45211</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45215</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45215</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45215</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45215</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45215</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45215</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45215</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45215</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45216</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45216</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45216</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45216</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>45216</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45216</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
         <v>45216</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45216</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45216</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45217</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45217</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45217</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>45217</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>45222</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45225</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>45226</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45230</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45230</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45236</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45238</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64022,14 +64022,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 55909-2023</t>
+          <t>A 55911-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64042,7 +64042,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -64086,7 +64086,7 @@
         <v>45239</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64136,14 +64136,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 55911-2023</t>
+          <t>A 55909-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64156,7 +64156,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64200,7 +64200,7 @@
         <v>45242</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45243</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>45244</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45244</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>45247</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>45249</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64535,14 +64535,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 58245-2023</t>
+          <t>A 58262-2023</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -64592,14 +64592,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 58262-2023</t>
+          <t>A 58245-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64656,7 +64656,7 @@
         <v>45250</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>45251</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45251</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64820,14 +64820,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 59220-2023</t>
+          <t>A 59289-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -64877,14 +64877,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 59333-2023</t>
+          <t>A 59220-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -64934,14 +64934,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 59289-2023</t>
+          <t>A 59333-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -64998,7 +64998,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -65055,7 +65055,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -65105,14 +65105,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59818-2023</t>
+          <t>A 59963-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -65125,7 +65125,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>3.2</v>
+        <v>25.3</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -65162,14 +65162,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59963-2023</t>
+          <t>A 59818-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -65182,7 +65182,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>25.3</v>
+        <v>3.2</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -65216,7 +65216,7 @@
       </c>
       <c r="R1060" s="2" t="inlineStr"/>
     </row>
-    <row r="1061">
+    <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
           <t>A 60645-2023</t>
@@ -65226,7 +65226,7 @@
         <v>45260</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45261</v>
+        <v>45262</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -65272,6 +65272,177 @@
         <v>0</v>
       </c>
       <c r="R1061" s="2" t="inlineStr"/>
+    </row>
+    <row r="1062" ht="15" customHeight="1">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>A 61105-2023</t>
+        </is>
+      </c>
+      <c r="B1062" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C1062" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>UMEÅ</t>
+        </is>
+      </c>
+      <c r="G1062" t="n">
+        <v>4</v>
+      </c>
+      <c r="H1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1062" s="2" t="inlineStr"/>
+    </row>
+    <row r="1063" ht="15" customHeight="1">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>A 61101-2023</t>
+        </is>
+      </c>
+      <c r="B1063" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C1063" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>UMEÅ</t>
+        </is>
+      </c>
+      <c r="G1063" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1063" s="2" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>A 60959-2023</t>
+        </is>
+      </c>
+      <c r="B1064" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="C1064" s="1" t="n">
+        <v>45262</v>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>UMEÅ</t>
+        </is>
+      </c>
+      <c r="G1064" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1064" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44410</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44410</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44410</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44410</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>44410</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44410</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44410</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44410</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44410</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44410</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44410</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44410</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44419</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44421</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44427</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44432</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44433</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44438</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44447</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44452</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44452</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44453</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44455</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>44456</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44456</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44460</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44462</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44464</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44464</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44463</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44467</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44469</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44470</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44473</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44473</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44476</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44476</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44480</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>44481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44483</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>44488</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44488</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44489</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44495</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>44496</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44502</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>44503</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44504</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44511</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44515</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44515</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>44529</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44533</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44533</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>44543</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44543</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>44550</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44550</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44550</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44550</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44560</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44566</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>44574</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44580</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44581</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44587</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44588</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44594</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44596</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44599</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44599</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44600</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44606</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>44606</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44606</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44606</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44606</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44606</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44606</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44606</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>44609</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>44610</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44610</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>44619</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44619</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44620</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44628</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44631</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44642</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44653</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44653</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>44670</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44672</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44679</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>44679</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44687</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44701</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44706</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>44714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>44715</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44715</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44727</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44729</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44729</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44729</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44731</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44734</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44740</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44740</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44740</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44742</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44742</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44750</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44756</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44772</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44772</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44774</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44774</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>44774</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44777</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44781</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44784</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44784</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44785</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>44788</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44790</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44792</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44797</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44798</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44802</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>44802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>44804</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44805</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44805</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44810</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44811</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44813</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>44813</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44813</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>44816</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>44816</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44816</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44817</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44818</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>44818</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44820</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44824</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>44825</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>44825</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>44830</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>44830</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44830</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44838</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44838</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>44838</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>44838</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>44839</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44839</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44839</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>44840</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>44840</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>44840</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>44841</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44841</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44840</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44841</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>44841</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44841</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44841</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44844</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>44846</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44846</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44846</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44846</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>44846</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44846</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44847</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44847</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44848</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44848</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44851</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44853</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44855</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44858</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44859</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44859</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>44859</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44859</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44860</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>44861</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44861</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44861</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>44862</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44865</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44865</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44865</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44867</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44872</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>44872</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44873</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44873</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44873</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44874</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>44874</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>44874</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>44874</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44876</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44876</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44876</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44876</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44896</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44896</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44896</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44900</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44900</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44900</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>44900</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44902</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44902</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44904</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44908</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>44914</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>44914</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>44914</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44917</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>44920</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44929</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44929</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44931</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44931</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44937</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44939</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44944</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44944</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>44944</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44944</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44944</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44944</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44949</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44953</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44957</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44958</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>44958</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44967</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>44972</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44977</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44980</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44980</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44981</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44981</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44983</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>44984</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44987</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44988</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45006</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45007</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45007</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45009</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45012</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45013</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45014</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45015</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45016</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45016</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45016</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45016</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45016</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45016</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45017</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45019</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45022</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45028</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45029</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45030</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45033</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45034</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45033</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45034</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45034</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45034</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45040</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45041</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45041</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45041</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45041</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45042</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45043</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45043</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45043</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45047</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45048</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45048</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45055</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45056</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45056</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45058</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45065</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45065</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45069</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45068</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45070</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45070</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45071</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45071</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45076</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45077</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45077</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45077</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45078</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45078</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45078</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45082</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45084</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45084</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45085</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45086</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45086</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45088</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45089</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45089</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45089</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45091</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45091</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45091</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45091</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45091</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45096</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45096</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45096</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45096</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45096</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45098</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45099</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45099</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45099</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45099</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45103</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45105</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45106</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45106</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45107</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45107</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45110</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45110</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45110</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45111</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45112</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45113</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45114</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45114</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45116</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45121</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45121</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45121</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45121</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45128</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45138</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45140</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45140</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45140</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45141</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45142</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45145</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45154</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45160</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45160</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45160</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45163</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45165</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45166</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45166</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45166</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45166</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45167</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45167</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45167</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45167</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45167</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45167</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45167</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45167</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45168</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45168</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45173</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45173</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45173</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45173</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45173</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45174</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45174</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45175</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45176</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45176</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45177</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45180</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45181</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45182</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45183</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45183</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45188</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45188</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45189</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45189</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45191</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45194</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45197</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45197</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45197</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45198</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45198</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45198</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45198</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45199</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45202</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45202</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45202</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45202</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45202</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45202</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45204</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45204</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>45205</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45208</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45208</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45209</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45209</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45210</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45211</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45211</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45211</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45215</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45215</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45215</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45215</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45215</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45215</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45215</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45215</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45216</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45216</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45216</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45216</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>45216</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45216</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
         <v>45216</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45216</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45216</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45217</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45217</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45217</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>45217</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>45222</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45225</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>45226</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45230</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45230</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45236</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45238</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>45239</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64079,14 +64079,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 55790-2023</t>
+          <t>A 55909-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64099,7 +64099,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -64136,14 +64136,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 55909-2023</t>
+          <t>A 55790-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64156,7 +64156,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64200,7 +64200,7 @@
         <v>45242</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45243</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64307,14 +64307,14 @@
     <row r="1045" ht="15" customHeight="1">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>A 56743-2023</t>
+          <t>A 56749-2023</t>
         </is>
       </c>
       <c r="B1045" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64327,7 +64327,7 @@
         </is>
       </c>
       <c r="G1045" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -64364,14 +64364,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 56749-2023</t>
+          <t>A 56743-2023</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -64428,7 +64428,7 @@
         <v>45247</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>45249</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64542,7 +64542,7 @@
         <v>45250</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64599,7 +64599,7 @@
         <v>45250</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64656,7 +64656,7 @@
         <v>45250</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>45251</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45251</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64820,14 +64820,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 59289-2023</t>
+          <t>A 59228-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -64884,7 +64884,7 @@
         <v>45252</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -64941,7 +64941,7 @@
         <v>45252</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -64991,14 +64991,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 59228-2023</t>
+          <t>A 59289-2023</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -65011,7 +65011,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -65055,7 +65055,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -65105,14 +65105,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59963-2023</t>
+          <t>A 59818-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -65125,7 +65125,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>25.3</v>
+        <v>3.2</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -65162,14 +65162,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59818-2023</t>
+          <t>A 59963-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -65182,7 +65182,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>3.2</v>
+        <v>25.3</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -65226,7 +65226,7 @@
         <v>45260</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -65276,14 +65276,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 61105-2023</t>
+          <t>A 61101-2023</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -65333,14 +65333,14 @@
     <row r="1063" ht="15" customHeight="1">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>A 61101-2023</t>
+          <t>A 60959-2023</t>
         </is>
       </c>
       <c r="B1063" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -65353,7 +65353,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>4.1</v>
+        <v>2.3</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -65390,14 +65390,14 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>A 60959-2023</t>
+          <t>A 61105-2023</t>
         </is>
       </c>
       <c r="B1064" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45262</v>
+        <v>45263</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -65410,7 +65410,7 @@
         </is>
       </c>
       <c r="G1064" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44410</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44410</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44410</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44410</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>44410</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44410</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44410</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44410</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44410</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44410</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44410</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44410</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44419</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44421</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44427</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44432</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44433</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44438</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44447</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44452</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44452</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44453</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44455</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>44456</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44456</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44460</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44462</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44464</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44464</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44463</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44467</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44469</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44470</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44473</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44473</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44476</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44476</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44480</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>44481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44483</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>44488</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44488</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44489</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44495</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>44496</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44502</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>44503</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44504</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44511</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44515</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44515</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>44529</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44533</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44533</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>44543</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44543</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>44550</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44550</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44550</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44550</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44560</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44566</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>44574</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44580</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44581</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44587</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44588</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44594</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44596</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44599</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44599</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44600</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44606</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>44606</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44606</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44606</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44606</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44606</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44606</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44606</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>44609</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>44610</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44610</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>44619</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44619</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44620</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44628</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44631</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44642</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44653</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44653</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>44670</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44672</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44679</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>44679</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44687</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44701</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44706</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>44714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>44715</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44715</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44727</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44729</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44729</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44729</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44731</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44734</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44740</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44740</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44740</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44742</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44742</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44750</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44756</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44772</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44772</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44774</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44774</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>44774</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44777</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44781</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44784</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44784</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44785</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>44788</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44790</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44792</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44797</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44798</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44802</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>44802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>44804</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44805</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44805</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44810</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44811</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44813</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>44813</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44813</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>44816</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>44816</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44816</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44817</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44818</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>44818</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44820</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44824</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>44825</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>44825</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>44830</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>44830</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44830</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44838</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44838</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>44838</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>44838</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>44839</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44839</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44839</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>44840</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>44840</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>44840</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>44841</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44841</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44840</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44841</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>44841</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44841</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44841</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44844</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>44846</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44846</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44846</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44846</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>44846</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44846</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44847</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44847</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44848</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44848</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44851</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44853</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44855</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44858</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44859</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44859</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>44859</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44859</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44860</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>44861</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44861</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44861</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>44862</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44865</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44865</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44865</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44867</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44872</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>44872</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44873</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44873</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44873</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44874</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>44874</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>44874</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>44874</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44876</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44876</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44876</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44876</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44896</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44896</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44896</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44900</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44900</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44900</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>44900</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44902</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44902</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44904</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44908</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>44914</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>44914</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>44914</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44917</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>44920</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44929</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44929</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44931</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44931</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44937</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44939</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44944</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44944</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>44944</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44944</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44944</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44944</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44949</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44953</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44957</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44958</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>44958</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44967</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>44972</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44977</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44980</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44980</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44981</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44981</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44983</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>44984</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44987</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44988</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45006</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45007</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45007</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45009</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45012</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45013</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45014</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45015</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45016</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45016</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45016</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45016</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45016</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45016</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45017</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45019</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45022</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45028</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45029</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45030</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45033</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45034</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45033</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45034</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45034</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45034</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45040</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45041</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45041</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45041</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45041</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45042</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45043</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45043</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45043</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45047</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45048</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45048</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45055</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45056</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45056</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45058</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45065</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45065</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45069</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45068</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45070</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45070</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45071</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45071</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45076</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45077</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45077</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45077</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45078</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45078</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45078</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45082</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45084</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45084</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45085</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45086</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45086</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45088</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45089</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45089</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45089</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45091</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45091</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45091</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45091</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45091</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45096</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45096</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45096</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45096</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45096</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45098</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45099</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45099</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45099</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45099</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45103</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45105</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45106</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45106</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45107</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45107</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45110</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45110</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45110</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45111</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45112</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45113</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45114</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45114</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45116</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45121</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45121</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45121</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45121</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45128</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45138</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45140</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45140</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45140</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45141</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45142</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45145</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45154</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45160</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45160</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45160</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45163</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45165</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45166</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45166</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45166</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45166</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45167</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45167</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45167</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45167</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45167</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45167</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45167</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45167</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45168</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45168</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45173</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45173</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45173</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45173</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45173</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45174</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45174</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45175</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45176</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45176</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45177</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45180</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45181</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45182</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45183</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45183</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45188</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45188</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45189</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45189</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45191</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45194</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45197</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45197</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45197</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45198</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45198</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45198</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45198</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45199</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45202</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45202</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45202</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45202</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45202</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45202</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45204</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45204</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>45205</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45208</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45208</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45209</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45209</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45210</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45211</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45211</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45211</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45215</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45215</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45215</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45215</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45215</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45215</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45215</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45215</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45216</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45216</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45216</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45216</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>45216</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45216</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
         <v>45216</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45216</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45216</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45217</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45217</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45217</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>45217</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>45222</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45225</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>45226</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45230</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45230</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45236</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45238</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64022,14 +64022,14 @@
     <row r="1040" ht="15" customHeight="1">
       <c r="A1040" t="inlineStr">
         <is>
-          <t>A 55911-2023</t>
+          <t>A 55790-2023</t>
         </is>
       </c>
       <c r="B1040" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64042,7 +64042,7 @@
         </is>
       </c>
       <c r="G1040" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="H1040" t="n">
         <v>0</v>
@@ -64079,14 +64079,14 @@
     <row r="1041" ht="15" customHeight="1">
       <c r="A1041" t="inlineStr">
         <is>
-          <t>A 55909-2023</t>
+          <t>A 55911-2023</t>
         </is>
       </c>
       <c r="B1041" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64099,7 +64099,7 @@
         </is>
       </c>
       <c r="G1041" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="H1041" t="n">
         <v>0</v>
@@ -64136,14 +64136,14 @@
     <row r="1042" ht="15" customHeight="1">
       <c r="A1042" t="inlineStr">
         <is>
-          <t>A 55790-2023</t>
+          <t>A 55909-2023</t>
         </is>
       </c>
       <c r="B1042" s="1" t="n">
         <v>45239</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64156,7 +64156,7 @@
         </is>
       </c>
       <c r="G1042" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="H1042" t="n">
         <v>0</v>
@@ -64200,7 +64200,7 @@
         <v>45242</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45243</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>45244</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45244</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>45247</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>45249</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64535,14 +64535,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 58262-2023</t>
+          <t>A 58245-2023</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -64592,14 +64592,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 58245-2023</t>
+          <t>A 58262-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>8.5</v>
+        <v>0.7</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64656,7 +64656,7 @@
         <v>45250</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>45251</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45251</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64820,14 +64820,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 59228-2023</t>
+          <t>A 59220-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -64877,14 +64877,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 59220-2023</t>
+          <t>A 59333-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -64934,14 +64934,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 59333-2023</t>
+          <t>A 59228-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -64998,7 +64998,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -65055,7 +65055,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45257</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -65169,7 +65169,7 @@
         <v>45257</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -65226,7 +65226,7 @@
         <v>45260</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -65276,14 +65276,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 61101-2023</t>
+          <t>A 61105-2023</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -65340,7 +65340,7 @@
         <v>45261</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -65390,14 +65390,14 @@
     <row r="1064">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>A 61105-2023</t>
+          <t>A 61101-2023</t>
         </is>
       </c>
       <c r="B1064" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45263</v>
+        <v>45264</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -65410,7 +65410,7 @@
         </is>
       </c>
       <c r="G1064" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1067"/>
+  <dimension ref="A1:Y1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="25"/>
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44410</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44410</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44410</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44410</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>44410</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44410</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44410</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44410</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44410</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44410</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44410</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44410</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44419</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44421</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44427</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44432</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44433</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44438</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44447</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44452</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44452</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44453</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44455</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>44456</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44456</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44460</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44462</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44464</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44464</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44463</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44467</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44469</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44470</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44473</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44473</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44476</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44476</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44480</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>44481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44483</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>44488</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44488</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44489</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44495</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>44496</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44502</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>44503</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44504</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44511</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44515</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44515</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>44529</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44533</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44533</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>44543</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44543</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>44550</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44550</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44550</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44550</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44560</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44566</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>44574</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44580</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44581</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44587</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44588</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44594</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44596</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44599</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44599</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44600</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44606</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>44606</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44606</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44606</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44606</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44606</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44606</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44606</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>44609</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>44610</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44610</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>44619</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44619</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44620</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44628</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44631</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44642</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44653</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44653</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>44670</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44672</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44679</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>44679</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44687</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44701</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44706</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>44714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>44715</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44715</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44727</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44729</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44729</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44729</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44731</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44734</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44740</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44740</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44740</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44742</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44742</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44750</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44756</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44772</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44772</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44774</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44774</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>44774</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44777</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44781</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44784</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44784</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44785</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>44788</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44790</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44792</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44797</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44798</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44802</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>44802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>44804</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44805</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44805</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44810</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44811</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44813</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>44813</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44813</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>44816</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>44816</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44816</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44817</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44818</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>44818</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44820</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44824</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>44825</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>44825</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>44830</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>44830</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44830</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44838</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44838</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>44838</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>44838</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>44839</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44839</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44839</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>44840</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>44840</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>44840</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>44841</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44841</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44840</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44841</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>44841</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44841</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44841</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44844</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>44846</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44846</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44846</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44846</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>44846</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44846</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44847</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44847</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44848</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44848</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44851</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44853</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44855</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44858</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44859</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44859</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>44859</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44859</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44860</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>44861</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44861</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44861</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>44862</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44865</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44865</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44865</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44867</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44872</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>44872</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44873</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44873</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44873</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44874</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>44874</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>44874</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>44874</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44876</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44876</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44876</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44876</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44896</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44896</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44896</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44900</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44900</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44900</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>44900</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44902</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44902</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44904</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44908</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>44914</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>44914</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>44914</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44917</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>44920</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44929</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44929</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44931</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44931</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44937</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44939</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44944</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44944</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>44944</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44944</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44944</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44944</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44949</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44953</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44957</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44958</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>44958</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44967</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>44972</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44977</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44980</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44980</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44981</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44981</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44983</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>44984</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44987</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44988</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45006</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45007</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45007</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45009</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45012</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45013</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45014</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45015</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45016</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45016</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45016</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45016</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45016</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45016</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45017</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45019</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45022</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45028</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45029</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45030</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45033</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45034</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45033</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45034</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45034</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45034</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45040</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45041</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45041</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45041</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45041</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45042</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45043</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45043</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45043</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45047</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45048</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45048</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45055</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45056</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45056</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45058</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45065</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45065</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45069</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45068</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45070</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45070</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45071</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45071</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45076</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45077</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45077</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45077</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45078</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45078</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45078</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45082</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45084</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45084</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45085</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45086</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45086</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45088</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45089</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45089</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45089</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45091</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45091</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45091</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45091</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45091</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45096</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45096</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45096</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45096</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45096</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45098</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45099</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45099</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45099</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45099</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45103</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45105</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45106</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45106</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45107</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45107</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45110</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45110</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45110</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45111</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45112</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45113</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45114</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45114</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45116</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45121</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45121</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45121</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45121</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45128</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45138</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45140</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45140</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45140</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45141</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45142</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45145</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45154</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45160</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45160</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45160</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45163</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45165</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45166</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45166</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45166</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45166</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45167</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45167</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45167</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45167</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45167</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45167</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45167</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45167</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45168</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45168</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45173</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45173</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45173</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45173</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45173</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45174</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45174</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45175</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45176</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45176</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45177</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45180</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45181</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45182</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45183</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45183</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45188</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45188</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45189</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45189</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45191</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45194</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45197</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45197</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45197</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45198</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45198</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45198</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45198</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45199</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45202</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45202</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45202</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45202</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45202</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45202</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45204</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45204</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>45205</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45208</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45208</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45209</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45209</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45210</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45211</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45211</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45211</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45215</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45215</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45215</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45215</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45215</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45215</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45215</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45215</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45216</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45216</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45216</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45216</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>45216</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45216</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
         <v>45216</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45216</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45216</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45217</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45217</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45217</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>45217</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>45222</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45225</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>45226</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45230</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45230</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45236</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45238</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>45239</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64086,7 +64086,7 @@
         <v>45239</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45239</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45242</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45243</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>45244</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45244</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>45247</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>45249</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64535,14 +64535,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 58256-2023</t>
+          <t>A 58262-2023</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -64592,14 +64592,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 58262-2023</t>
+          <t>A 58256-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64656,7 +64656,7 @@
         <v>45250</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64713,7 +64713,7 @@
         <v>45251</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64770,7 +64770,7 @@
         <v>45251</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64820,14 +64820,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 59289-2023</t>
+          <t>A 59220-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>2</v>
+        <v>4.4</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -64877,14 +64877,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 59228-2023</t>
+          <t>A 59333-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -64934,14 +64934,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 59220-2023</t>
+          <t>A 59289-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -64991,14 +64991,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 59333-2023</t>
+          <t>A 59228-2023</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -65011,7 +65011,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -65055,7 +65055,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -65105,14 +65105,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59963-2023</t>
+          <t>A 59818-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -65125,7 +65125,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>25.3</v>
+        <v>3.2</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -65162,14 +65162,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59818-2023</t>
+          <t>A 59963-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -65182,7 +65182,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>3.2</v>
+        <v>25.3</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -65226,7 +65226,7 @@
         <v>45260</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -65276,14 +65276,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 61204-2023</t>
+          <t>A 61280-2023</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -65340,7 +65340,7 @@
         <v>45260</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -65390,14 +65390,14 @@
     <row r="1064" ht="15" customHeight="1">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>A 61280-2023</t>
+          <t>A 61204-2023</t>
         </is>
       </c>
       <c r="B1064" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -65410,7 +65410,7 @@
         </is>
       </c>
       <c r="G1064" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>
@@ -65454,7 +65454,7 @@
         <v>45261</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -65504,14 +65504,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 61101-2023</t>
+          <t>A 61105-2023</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -65524,7 +65524,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -65558,17 +65558,17 @@
       </c>
       <c r="R1066" s="2" t="inlineStr"/>
     </row>
-    <row r="1067">
+    <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 61105-2023</t>
+          <t>A 61101-2023</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45265</v>
+        <v>45266</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -65581,7 +65581,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -65614,6 +65614,120 @@
         <v>0</v>
       </c>
       <c r="R1067" s="2" t="inlineStr"/>
+    </row>
+    <row r="1068" ht="15" customHeight="1">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>A 61749-2023</t>
+        </is>
+      </c>
+      <c r="B1068" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C1068" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>UMEÅ</t>
+        </is>
+      </c>
+      <c r="G1068" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1068" s="2" t="inlineStr"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>A 61703-2023</t>
+        </is>
+      </c>
+      <c r="B1069" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="C1069" s="1" t="n">
+        <v>45266</v>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>VÄSTERBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>UMEÅ</t>
+        </is>
+      </c>
+      <c r="G1069" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1069" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44410</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44410</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44410</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44410</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>44410</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44410</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44410</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44410</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44410</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44410</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44410</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44410</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44419</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44421</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44427</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44432</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44433</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44438</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44447</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44452</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44452</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44453</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44455</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>44456</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44456</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44460</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44462</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44464</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44464</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44463</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44467</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44469</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44470</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44473</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44473</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44476</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44476</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44480</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>44481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44483</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>44488</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44488</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44489</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44495</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>44496</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44502</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>44503</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44504</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44511</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44515</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44515</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>44529</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44533</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44533</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>44543</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44543</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>44550</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44550</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44550</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44550</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44560</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44566</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>44574</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44580</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44581</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44587</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44588</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44594</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44596</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44599</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44599</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44600</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44606</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>44606</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44606</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44606</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44606</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44606</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44606</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44606</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>44609</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>44610</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44610</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>44619</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44619</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44620</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44628</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44631</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44642</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44653</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44653</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>44670</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44672</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44679</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>44679</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44687</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44701</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44706</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>44714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>44715</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44715</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44727</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44729</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44729</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44729</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44731</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44734</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44740</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44740</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44740</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44742</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44742</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44750</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44756</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44772</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44772</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44774</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44774</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>44774</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44777</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44781</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44784</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44784</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44785</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>44788</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44790</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44792</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44797</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44798</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44802</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>44802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>44804</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44805</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44805</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44810</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44811</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44813</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>44813</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44813</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>44816</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>44816</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44816</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44817</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44818</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>44818</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44820</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44824</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>44825</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>44825</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>44830</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>44830</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44830</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44838</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44838</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>44838</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>44838</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>44839</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44839</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44839</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>44840</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>44840</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>44840</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>44841</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44841</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44840</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44841</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>44841</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44841</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44841</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44844</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>44846</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44846</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44846</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44846</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>44846</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44846</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44847</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44847</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44848</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44848</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44851</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44853</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44855</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44858</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44859</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44859</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>44859</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44859</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44860</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>44861</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44861</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44861</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>44862</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44865</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44865</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44865</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44867</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44872</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>44872</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44873</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44873</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44873</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44874</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>44874</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>44874</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>44874</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44876</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44876</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44876</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44876</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44896</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44896</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44896</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44900</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44900</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44900</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>44900</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44902</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44902</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44904</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44908</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>44914</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>44914</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>44914</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44917</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>44920</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44929</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44929</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44931</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44931</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44937</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44939</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44944</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44944</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>44944</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44944</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44944</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44944</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44949</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44953</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44957</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44958</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>44958</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44967</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>44972</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44977</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44980</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44980</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44981</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44981</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44983</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>44984</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44987</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44988</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45006</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45007</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45007</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45009</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45012</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45013</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45014</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45015</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45016</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45016</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45016</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45016</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45016</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45016</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45017</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45019</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45022</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45028</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45029</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45030</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45033</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45034</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45033</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45034</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45034</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45034</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45040</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45041</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45041</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45041</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45041</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45042</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45043</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45043</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45043</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45047</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45048</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45048</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45055</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45056</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45056</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45058</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45065</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45065</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45069</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45068</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45070</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45070</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45071</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45071</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45076</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45077</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45077</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45077</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45078</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45078</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45078</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45082</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45084</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45084</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45085</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45086</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45086</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45088</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45089</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45089</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45089</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45091</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45091</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45091</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45091</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45091</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45096</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45096</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45096</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45096</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45096</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45098</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45099</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45099</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45099</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45099</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45103</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45105</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45106</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45106</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45107</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45107</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45110</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45110</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45110</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45111</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45112</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45113</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45114</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45114</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45116</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45121</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45121</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45121</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45121</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45128</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45138</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45140</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45140</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45140</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45141</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45142</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45145</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45154</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45160</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45160</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45160</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45163</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45165</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45166</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45166</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45166</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45166</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45167</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45167</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45167</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45167</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45167</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45167</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45167</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45167</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45168</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45168</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45173</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45173</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45173</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45173</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45173</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45174</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45174</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45175</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45176</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45176</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45177</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45180</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45181</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45182</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45183</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45183</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45188</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45188</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45189</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45189</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45191</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45194</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45197</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45197</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45197</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45198</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45198</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45198</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45198</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45199</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45202</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45202</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45202</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45202</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45202</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45202</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45204</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45204</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>45205</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45208</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45208</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45209</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45209</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45210</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45211</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45211</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45211</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45215</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45215</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45215</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45215</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45215</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45215</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45215</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45215</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45216</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45216</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45216</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45216</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>45216</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45216</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
         <v>45216</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45216</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45216</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45217</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45217</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45217</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>45217</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>45222</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45225</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>45226</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45230</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45230</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45236</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45238</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>45239</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64086,7 +64086,7 @@
         <v>45239</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45239</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45242</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45243</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64307,14 +64307,14 @@
     <row r="1045" ht="15" customHeight="1">
       <c r="A1045" t="inlineStr">
         <is>
-          <t>A 56749-2023</t>
+          <t>A 56743-2023</t>
         </is>
       </c>
       <c r="B1045" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64327,7 +64327,7 @@
         </is>
       </c>
       <c r="G1045" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="H1045" t="n">
         <v>0</v>
@@ -64364,14 +64364,14 @@
     <row r="1046" ht="15" customHeight="1">
       <c r="A1046" t="inlineStr">
         <is>
-          <t>A 56743-2023</t>
+          <t>A 56749-2023</t>
         </is>
       </c>
       <c r="B1046" s="1" t="n">
         <v>45244</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         </is>
       </c>
       <c r="G1046" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1046" t="n">
         <v>0</v>
@@ -64428,7 +64428,7 @@
         <v>45247</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>45249</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64535,14 +64535,14 @@
     <row r="1049" ht="15" customHeight="1">
       <c r="A1049" t="inlineStr">
         <is>
-          <t>A 58262-2023</t>
+          <t>A 58245-2023</t>
         </is>
       </c>
       <c r="B1049" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         </is>
       </c>
       <c r="G1049" t="n">
-        <v>0.7</v>
+        <v>8.5</v>
       </c>
       <c r="H1049" t="n">
         <v>0</v>
@@ -64592,14 +64592,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 58256-2023</t>
+          <t>A 58262-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64649,14 +64649,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 58245-2023</t>
+          <t>A 58256-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64669,7 +64669,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>8.5</v>
+        <v>0.3</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64706,14 +64706,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 59152-2023</t>
+          <t>A 59157-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64763,14 +64763,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 59157-2023</t>
+          <t>A 59152-2023</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -64827,7 +64827,7 @@
         <v>45252</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64877,14 +64877,14 @@
     <row r="1055" ht="15" customHeight="1">
       <c r="A1055" t="inlineStr">
         <is>
-          <t>A 59333-2023</t>
+          <t>A 59289-2023</t>
         </is>
       </c>
       <c r="B1055" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -64897,7 +64897,7 @@
         </is>
       </c>
       <c r="G1055" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1055" t="n">
         <v>0</v>
@@ -64934,14 +64934,14 @@
     <row r="1056" ht="15" customHeight="1">
       <c r="A1056" t="inlineStr">
         <is>
-          <t>A 59289-2023</t>
+          <t>A 59333-2023</t>
         </is>
       </c>
       <c r="B1056" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -64954,7 +64954,7 @@
         </is>
       </c>
       <c r="G1056" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1056" t="n">
         <v>0</v>
@@ -64998,7 +64998,7 @@
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -65055,7 +65055,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -65112,7 +65112,7 @@
         <v>45257</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -65169,7 +65169,7 @@
         <v>45257</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -65219,14 +65219,14 @@
     <row r="1061" ht="15" customHeight="1">
       <c r="A1061" t="inlineStr">
         <is>
-          <t>A 60645-2023</t>
+          <t>A 61280-2023</t>
         </is>
       </c>
       <c r="B1061" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -65239,7 +65239,7 @@
         </is>
       </c>
       <c r="G1061" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="H1061" t="n">
         <v>0</v>
@@ -65276,14 +65276,14 @@
     <row r="1062" ht="15" customHeight="1">
       <c r="A1062" t="inlineStr">
         <is>
-          <t>A 61280-2023</t>
+          <t>A 60645-2023</t>
         </is>
       </c>
       <c r="B1062" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -65296,7 +65296,7 @@
         </is>
       </c>
       <c r="G1062" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -65333,14 +65333,14 @@
     <row r="1063" ht="15" customHeight="1">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>A 61275-2023</t>
+          <t>A 61204-2023</t>
         </is>
       </c>
       <c r="B1063" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -65353,7 +65353,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -65390,14 +65390,14 @@
     <row r="1064" ht="15" customHeight="1">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>A 61204-2023</t>
+          <t>A 61275-2023</t>
         </is>
       </c>
       <c r="B1064" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -65410,7 +65410,7 @@
         </is>
       </c>
       <c r="G1064" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>
@@ -65454,7 +65454,7 @@
         <v>45261</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -65511,7 +65511,7 @@
         <v>45261</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -65568,7 +65568,7 @@
         <v>45261</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -65618,14 +65618,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 61749-2023</t>
+          <t>A 61703-2023</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -65675,14 +65675,14 @@
     <row r="1069">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 61703-2023</t>
+          <t>A 61749-2023</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45266</v>
+        <v>45267</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -65695,7 +65695,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33418,7 +33418,7 @@
         <v>44410</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33480,7 +33480,7 @@
         <v>44410</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44410</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33604,7 +33604,7 @@
         <v>44410</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33666,7 +33666,7 @@
         <v>44410</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>44410</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>44410</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>44410</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>44410</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>44410</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>44410</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34100,7 +34100,7 @@
         <v>44410</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>44419</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>44421</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34286,7 +34286,7 @@
         <v>44427</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>44432</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44433</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44438</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34514,7 +34514,7 @@
         <v>44447</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>44447</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>44452</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>44452</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44453</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>44453</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44455</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>44456</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>44456</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35027,7 +35027,7 @@
         <v>44460</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>44462</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44464</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>44464</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>44463</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>44467</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>44467</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>44469</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>44470</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>44473</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>44473</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>44476</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35741,7 +35741,7 @@
         <v>44476</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44480</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>44481</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35917,7 +35917,7 @@
         <v>44481</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35979,7 +35979,7 @@
         <v>44482</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>44483</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>44488</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44488</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>44489</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44495</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>44496</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44502</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>44503</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44504</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44511</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>44515</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44515</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>44529</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>44533</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44533</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>44543</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>44543</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>44550</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37087,7 +37087,7 @@
         <v>44550</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
         <v>44550</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>44550</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44560</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>44566</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>44574</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37429,7 +37429,7 @@
         <v>44580</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>44580</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44581</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>44587</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>44588</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>44592</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         <v>44592</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37890,7 +37890,7 @@
         <v>44594</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37947,7 +37947,7 @@
         <v>44596</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>44599</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>44599</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>44600</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>44602</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>44606</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>44606</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>44606</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44606</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38465,7 +38465,7 @@
         <v>44606</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38522,7 +38522,7 @@
         <v>44606</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>44606</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38636,7 +38636,7 @@
         <v>44606</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44606</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38750,7 +38750,7 @@
         <v>44606</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38807,7 +38807,7 @@
         <v>44609</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>44610</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>44610</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38978,7 +38978,7 @@
         <v>44617</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39035,7 +39035,7 @@
         <v>44619</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44619</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39149,7 +39149,7 @@
         <v>44620</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>44628</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>44629</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39382,7 +39382,7 @@
         <v>44631</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>44631</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44642</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>44653</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44653</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>44666</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>44670</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39796,7 +39796,7 @@
         <v>44672</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>44679</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>44679</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44687</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>44701</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40091,7 +40091,7 @@
         <v>44706</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>44714</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>44715</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>44715</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>44727</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>44729</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44729</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44729</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>44731</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>44734</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44740</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44740</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>44740</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>44741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44742</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>44742</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41008,7 +41008,7 @@
         <v>44750</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>44756</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44772</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>44772</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41241,7 +41241,7 @@
         <v>44774</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41298,7 +41298,7 @@
         <v>44774</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>44774</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41417,7 +41417,7 @@
         <v>44777</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41474,7 +41474,7 @@
         <v>44781</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>44784</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>44784</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41650,7 +41650,7 @@
         <v>44785</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41712,7 +41712,7 @@
         <v>44788</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44790</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>44792</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>44797</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>44798</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42007,7 +42007,7 @@
         <v>44802</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42064,7 +42064,7 @@
         <v>44802</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42121,7 +42121,7 @@
         <v>44804</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44805</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44805</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44810</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>44811</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44811</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
         <v>44813</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>44813</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>44813</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42669,7 +42669,7 @@
         <v>44816</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42731,7 +42731,7 @@
         <v>44816</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44816</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44817</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42912,7 +42912,7 @@
         <v>44817</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42974,7 +42974,7 @@
         <v>44818</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>44818</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43093,7 +43093,7 @@
         <v>44818</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43150,7 +43150,7 @@
         <v>44820</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>44824</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>44825</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43321,7 +43321,7 @@
         <v>44825</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43378,7 +43378,7 @@
         <v>44830</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43435,7 +43435,7 @@
         <v>44830</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43492,7 +43492,7 @@
         <v>44830</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43554,7 +43554,7 @@
         <v>44838</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44838</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>44838</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>44838</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43787,7 +43787,7 @@
         <v>44839</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>44839</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>44839</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44015,7 +44015,7 @@
         <v>44839</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44072,7 +44072,7 @@
         <v>44840</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44134,7 +44134,7 @@
         <v>44840</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44191,7 +44191,7 @@
         <v>44841</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>44840</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>44841</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44362,7 +44362,7 @@
         <v>44841</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44476,7 +44476,7 @@
         <v>44840</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>44841</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44590,7 +44590,7 @@
         <v>44841</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>44841</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>44841</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44766,7 +44766,7 @@
         <v>44844</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44823,7 +44823,7 @@
         <v>44846</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>44846</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>44846</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>44846</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45051,7 +45051,7 @@
         <v>44846</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>44846</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45165,7 +45165,7 @@
         <v>44847</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45222,7 +45222,7 @@
         <v>44847</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44848</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>44848</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44851</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>44853</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>44854</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>44855</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44858</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>44859</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>44859</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>44859</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45874,7 +45874,7 @@
         <v>44859</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>44860</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45988,7 +45988,7 @@
         <v>44861</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46050,7 +46050,7 @@
         <v>44861</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46107,7 +46107,7 @@
         <v>44861</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46169,7 +46169,7 @@
         <v>44862</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44865</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46293,7 +46293,7 @@
         <v>44865</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46350,7 +46350,7 @@
         <v>44865</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>44867</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>44872</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>44872</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>44873</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>44873</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -46697,7 +46697,7 @@
         <v>44873</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46754,7 +46754,7 @@
         <v>44873</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46811,7 +46811,7 @@
         <v>44874</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46873,7 +46873,7 @@
         <v>44874</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>44874</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46997,7 +46997,7 @@
         <v>44874</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>44876</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>44876</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>44876</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44876</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>44889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47359,7 +47359,7 @@
         <v>44896</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47421,7 +47421,7 @@
         <v>44896</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>44896</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47535,7 +47535,7 @@
         <v>44900</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>44900</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47649,7 +47649,7 @@
         <v>44900</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>44900</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>44902</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>44902</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47887,7 +47887,7 @@
         <v>44904</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44908</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>44908</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>44914</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>44914</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>44914</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>44916</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>44917</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48353,7 +48353,7 @@
         <v>44920</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>44929</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44929</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44931</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44931</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44937</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44939</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -48757,7 +48757,7 @@
         <v>44944</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48814,7 +48814,7 @@
         <v>44944</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>44944</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44944</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>44944</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>44944</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49099,7 +49099,7 @@
         <v>44946</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>44949</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>44953</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49275,7 +49275,7 @@
         <v>44957</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44958</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>44958</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44967</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>44972</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>44977</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44980</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>44980</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -49751,7 +49751,7 @@
         <v>44981</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>44981</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>44981</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>44983</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>44984</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50041,7 +50041,7 @@
         <v>44984</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>44987</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50155,7 +50155,7 @@
         <v>44988</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50212,7 +50212,7 @@
         <v>45006</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>45007</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>45007</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45009</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45009</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45012</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45013</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45014</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>45015</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>45016</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45016</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45016</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>45016</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45016</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51050,7 +51050,7 @@
         <v>45016</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51107,7 +51107,7 @@
         <v>45017</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51164,7 +51164,7 @@
         <v>45019</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45019</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>45022</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51350,7 +51350,7 @@
         <v>45022</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>45028</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45029</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45030</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51583,7 +51583,7 @@
         <v>45033</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45034</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51697,7 +51697,7 @@
         <v>45033</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>45033</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -51821,7 +51821,7 @@
         <v>45034</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>45034</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45034</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52054,7 +52054,7 @@
         <v>45037</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45037</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>45037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45040</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>45041</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45041</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52411,7 +52411,7 @@
         <v>45041</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52473,7 +52473,7 @@
         <v>45041</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45042</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45043</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45043</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52706,7 +52706,7 @@
         <v>45043</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52763,7 +52763,7 @@
         <v>45047</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>45048</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -52877,7 +52877,7 @@
         <v>45048</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45055</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45056</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>45056</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45058</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45065</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53219,7 +53219,7 @@
         <v>45065</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53276,7 +53276,7 @@
         <v>45069</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53333,7 +53333,7 @@
         <v>45068</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>45070</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45070</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45071</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45071</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45076</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53675,7 +53675,7 @@
         <v>45077</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53732,7 +53732,7 @@
         <v>45077</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45077</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -53846,7 +53846,7 @@
         <v>45078</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>45078</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -53965,7 +53965,7 @@
         <v>45078</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45078</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54079,7 +54079,7 @@
         <v>45078</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45082</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45084</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54255,7 +54255,7 @@
         <v>45084</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>45085</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54369,7 +54369,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54426,7 +54426,7 @@
         <v>45086</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45086</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54540,7 +54540,7 @@
         <v>45088</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45089</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45089</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45089</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>45091</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45091</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45091</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45091</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55006,7 +55006,7 @@
         <v>45091</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55063,7 +55063,7 @@
         <v>45096</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55120,7 +55120,7 @@
         <v>45096</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55177,7 +55177,7 @@
         <v>45096</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45096</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55291,7 +55291,7 @@
         <v>45096</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45098</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>45099</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55467,7 +55467,7 @@
         <v>45099</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45099</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55581,7 +55581,7 @@
         <v>45099</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55638,7 +55638,7 @@
         <v>45103</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>45105</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>45106</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45106</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45107</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45107</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45110</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56052,7 +56052,7 @@
         <v>45110</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56114,7 +56114,7 @@
         <v>45110</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56176,7 +56176,7 @@
         <v>45111</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>45112</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45112</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56347,7 +56347,7 @@
         <v>45113</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45114</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45114</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45116</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56585,7 +56585,7 @@
         <v>45121</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45121</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45121</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>45121</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45128</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -56870,7 +56870,7 @@
         <v>45138</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -56932,7 +56932,7 @@
         <v>45140</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>45140</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57056,7 +57056,7 @@
         <v>45140</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57118,7 +57118,7 @@
         <v>45141</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57180,7 +57180,7 @@
         <v>45142</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57237,7 +57237,7 @@
         <v>45145</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57294,7 +57294,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>45154</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57522,7 +57522,7 @@
         <v>45160</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57584,7 +57584,7 @@
         <v>45160</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57641,7 +57641,7 @@
         <v>45160</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57698,7 +57698,7 @@
         <v>45161</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57755,7 +57755,7 @@
         <v>45162</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -57817,7 +57817,7 @@
         <v>45163</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>45165</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -57931,7 +57931,7 @@
         <v>45166</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -57988,7 +57988,7 @@
         <v>45166</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45166</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58102,7 +58102,7 @@
         <v>45166</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45167</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58221,7 +58221,7 @@
         <v>45167</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>45167</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45167</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58407,7 +58407,7 @@
         <v>45167</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58469,7 +58469,7 @@
         <v>45167</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45167</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58588,7 +58588,7 @@
         <v>45167</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45167</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58707,7 +58707,7 @@
         <v>45168</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58764,7 +58764,7 @@
         <v>45168</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45168</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45170</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>45171</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59059,7 +59059,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>45173</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>45173</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>45173</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45173</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>45173</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45174</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45174</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45175</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45176</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45176</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45177</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45180</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59835,7 +59835,7 @@
         <v>45180</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45181</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45182</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60016,7 +60016,7 @@
         <v>45183</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45183</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45188</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60192,7 +60192,7 @@
         <v>45188</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45188</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60311,7 +60311,7 @@
         <v>45189</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45189</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45191</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60497,7 +60497,7 @@
         <v>45194</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>45197</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60621,7 +60621,7 @@
         <v>45197</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45197</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60740,7 +60740,7 @@
         <v>45198</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60797,7 +60797,7 @@
         <v>45198</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45198</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45198</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>45198</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45198</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45198</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61139,7 +61139,7 @@
         <v>45199</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45202</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61253,7 +61253,7 @@
         <v>45202</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61310,7 +61310,7 @@
         <v>45202</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61367,7 +61367,7 @@
         <v>45202</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61424,7 +61424,7 @@
         <v>45202</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61481,7 +61481,7 @@
         <v>45202</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61538,7 +61538,7 @@
         <v>45204</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>45204</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61662,7 +61662,7 @@
         <v>45205</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61719,7 +61719,7 @@
         <v>45208</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61776,7 +61776,7 @@
         <v>45208</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>45209</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61890,7 +61890,7 @@
         <v>45209</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -61947,7 +61947,7 @@
         <v>45210</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62009,7 +62009,7 @@
         <v>45211</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45211</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62123,7 +62123,7 @@
         <v>45211</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>45215</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45215</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62294,7 +62294,7 @@
         <v>45215</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45215</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>45215</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62465,7 +62465,7 @@
         <v>45215</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62522,7 +62522,7 @@
         <v>45215</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62579,7 +62579,7 @@
         <v>45215</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62636,7 +62636,7 @@
         <v>45216</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62693,7 +62693,7 @@
         <v>45216</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62750,7 +62750,7 @@
         <v>45216</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62807,7 +62807,7 @@
         <v>45216</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45216</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -62921,7 +62921,7 @@
         <v>45216</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -62983,7 +62983,7 @@
         <v>45216</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63040,7 +63040,7 @@
         <v>45216</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63097,7 +63097,7 @@
         <v>45216</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>45216</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63211,7 +63211,7 @@
         <v>45217</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63273,7 +63273,7 @@
         <v>45217</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45217</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63392,7 +63392,7 @@
         <v>45217</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63449,7 +63449,7 @@
         <v>45222</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63506,7 +63506,7 @@
         <v>45222</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63563,7 +63563,7 @@
         <v>45225</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63620,7 +63620,7 @@
         <v>45225</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63677,7 +63677,7 @@
         <v>45226</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>45230</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>45230</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -63853,7 +63853,7 @@
         <v>45236</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -63910,7 +63910,7 @@
         <v>45237</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -63967,7 +63967,7 @@
         <v>45238</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>45239</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64086,7 +64086,7 @@
         <v>45239</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64143,7 +64143,7 @@
         <v>45239</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45242</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64257,7 +64257,7 @@
         <v>45243</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64314,7 +64314,7 @@
         <v>45244</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64371,7 +64371,7 @@
         <v>45244</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64428,7 +64428,7 @@
         <v>45247</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>45249</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64542,7 +64542,7 @@
         <v>45250</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64592,14 +64592,14 @@
     <row r="1050" ht="15" customHeight="1">
       <c r="A1050" t="inlineStr">
         <is>
-          <t>A 58256-2023</t>
+          <t>A 58245-2023</t>
         </is>
       </c>
       <c r="B1050" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64612,7 +64612,7 @@
         </is>
       </c>
       <c r="G1050" t="n">
-        <v>0.3</v>
+        <v>8.5</v>
       </c>
       <c r="H1050" t="n">
         <v>0</v>
@@ -64649,14 +64649,14 @@
     <row r="1051" ht="15" customHeight="1">
       <c r="A1051" t="inlineStr">
         <is>
-          <t>A 58245-2023</t>
+          <t>A 58256-2023</t>
         </is>
       </c>
       <c r="B1051" s="1" t="n">
         <v>45250</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64669,7 +64669,7 @@
         </is>
       </c>
       <c r="G1051" t="n">
-        <v>8.5</v>
+        <v>0.3</v>
       </c>
       <c r="H1051" t="n">
         <v>0</v>
@@ -64706,14 +64706,14 @@
     <row r="1052" ht="15" customHeight="1">
       <c r="A1052" t="inlineStr">
         <is>
-          <t>A 59157-2023</t>
+          <t>A 59152-2023</t>
         </is>
       </c>
       <c r="B1052" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         </is>
       </c>
       <c r="G1052" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="H1052" t="n">
         <v>0</v>
@@ -64763,14 +64763,14 @@
     <row r="1053" ht="15" customHeight="1">
       <c r="A1053" t="inlineStr">
         <is>
-          <t>A 59152-2023</t>
+          <t>A 59157-2023</t>
         </is>
       </c>
       <c r="B1053" s="1" t="n">
         <v>45251</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -64783,7 +64783,7 @@
         </is>
       </c>
       <c r="G1053" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="H1053" t="n">
         <v>0</v>
@@ -64820,14 +64820,14 @@
     <row r="1054" ht="15" customHeight="1">
       <c r="A1054" t="inlineStr">
         <is>
-          <t>A 59228-2023</t>
+          <t>A 59220-2023</t>
         </is>
       </c>
       <c r="B1054" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -64840,7 +64840,7 @@
         </is>
       </c>
       <c r="G1054" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="H1054" t="n">
         <v>0</v>
@@ -64884,7 +64884,7 @@
         <v>45252</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -64941,7 +64941,7 @@
         <v>45252</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -64991,14 +64991,14 @@
     <row r="1057" ht="15" customHeight="1">
       <c r="A1057" t="inlineStr">
         <is>
-          <t>A 59220-2023</t>
+          <t>A 59228-2023</t>
         </is>
       </c>
       <c r="B1057" s="1" t="n">
         <v>45252</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -65011,7 +65011,7 @@
         </is>
       </c>
       <c r="G1057" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="H1057" t="n">
         <v>0</v>
@@ -65055,7 +65055,7 @@
         <v>45253</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -65105,14 +65105,14 @@
     <row r="1059" ht="15" customHeight="1">
       <c r="A1059" t="inlineStr">
         <is>
-          <t>A 59963-2023</t>
+          <t>A 59818-2023</t>
         </is>
       </c>
       <c r="B1059" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -65125,7 +65125,7 @@
         </is>
       </c>
       <c r="G1059" t="n">
-        <v>25.3</v>
+        <v>3.2</v>
       </c>
       <c r="H1059" t="n">
         <v>0</v>
@@ -65162,14 +65162,14 @@
     <row r="1060" ht="15" customHeight="1">
       <c r="A1060" t="inlineStr">
         <is>
-          <t>A 59818-2023</t>
+          <t>A 59963-2023</t>
         </is>
       </c>
       <c r="B1060" s="1" t="n">
         <v>45257</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -65182,7 +65182,7 @@
         </is>
       </c>
       <c r="G1060" t="n">
-        <v>3.2</v>
+        <v>25.3</v>
       </c>
       <c r="H1060" t="n">
         <v>0</v>
@@ -65226,7 +65226,7 @@
         <v>45260</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -65283,7 +65283,7 @@
         <v>45260</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -65333,14 +65333,14 @@
     <row r="1063" ht="15" customHeight="1">
       <c r="A1063" t="inlineStr">
         <is>
-          <t>A 61280-2023</t>
+          <t>A 61204-2023</t>
         </is>
       </c>
       <c r="B1063" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -65353,7 +65353,7 @@
         </is>
       </c>
       <c r="G1063" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="H1063" t="n">
         <v>0</v>
@@ -65390,14 +65390,14 @@
     <row r="1064" ht="15" customHeight="1">
       <c r="A1064" t="inlineStr">
         <is>
-          <t>A 61204-2023</t>
+          <t>A 61280-2023</t>
         </is>
       </c>
       <c r="B1064" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -65410,7 +65410,7 @@
         </is>
       </c>
       <c r="G1064" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="H1064" t="n">
         <v>0</v>
@@ -65454,7 +65454,7 @@
         <v>45261</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -65504,14 +65504,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 61101-2023</t>
+          <t>A 61105-2023</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -65524,7 +65524,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -65561,14 +65561,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 61105-2023</t>
+          <t>A 61563-2023</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -65581,7 +65581,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -65618,14 +65618,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 61563-2023</t>
+          <t>A 61101-2023</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -65675,14 +65675,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 61703-2023</t>
+          <t>A 61749-2023</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -65695,7 +65695,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -65732,14 +65732,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 61749-2023</t>
+          <t>A 61703-2023</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45264</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -65752,7 +65752,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>2.4</v>
+        <v>7.3</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -65796,7 +65796,7 @@
         <v>45267</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -65853,7 +65853,7 @@
         <v>45268</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45269</v>
+        <v>45270</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>

--- a/Översikt UMEÅ.xlsx
+++ b/Översikt UMEÅ.xlsx
@@ -564,7 +564,7 @@
         <v>44821</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         <v>45184</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>43640</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         <v>44427</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44797</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>44868</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>44973</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>44826</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>45020</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>43641</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>43851</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>43895</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44117</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>44616</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>44679</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>44785</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>45110</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>44715</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>44867</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45014</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>43333</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>44060</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44157</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>44645</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>44819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45019</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45069</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>43846</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>43900</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44407</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>44407</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>44670</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>44785</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>45195</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>45209</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>43391</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         <v>43851</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>43901</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44068</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44320</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44615</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44714</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44862</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>44914</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4643,7 +4643,7 @@
         <v>44925</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45040</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>43483</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44068</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44384</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44406</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44406</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44407</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>44619</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>44839</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44874</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45043</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>45198</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45209</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>43479</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>43749</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>43966</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         <v>44102</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44117</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>44406</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>44406</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44406</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44406</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44410</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6834,7 +6834,7 @@
         <v>44410</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>44410</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>44455</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44631</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44673</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44715</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44733</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         <v>44837</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44862</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44904</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         <v>44993</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45019</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>45099</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45104</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45128</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         <v>45152</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>45165</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45176</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45189</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45251</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>43332</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         <v>43346</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>43350</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>43353</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>43353</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>43354</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>43355</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>43364</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>43368</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>43368</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>43368</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>43368</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>43370</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>43370</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>43374</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>43384</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>43384</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>43385</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>43385</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>43392</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>43392</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>43392</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>43405</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>43406</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>43409</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>43412</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>43413</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>43413</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>43415</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>43416</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>43416</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>43419</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>43419</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>43419</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>43422</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>43422</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>43423</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>43424</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>43424</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>43424</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>43426</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>43427</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>43433</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>43440</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>43444</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>43448</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>43451</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11382,7 +11382,7 @@
         <v>43451</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>43451</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>43452</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11553,7 +11553,7 @@
         <v>43454</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>43455</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>43455</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>43464</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>43467</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>43467</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>43473</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>43474</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>43474</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>43475</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>43475</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>43475</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>43476</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>43481</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>43482</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12423,7 +12423,7 @@
         <v>43487</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>43495</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>43495</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>43504</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>43509</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>43509</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>43516</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>43518</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>43518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>43518</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>43522</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>43535</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>43537</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>43538</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>43539</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>43549</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>43550</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>43553</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>43553</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>43556</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>43556</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>43572</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>43588</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>43591</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>43593</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>43593</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>43595</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>43605</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>43605</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>43606</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>43606</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>43613</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>43620</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>43623</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>43628</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>43628</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>43633</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>43634</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>43639</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>43639</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>43639</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>43640</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>43641</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>43642</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>43643</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>43649</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>43649</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>43650</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>43651</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>43651</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>43651</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>43693</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>43693</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15469,7 +15469,7 @@
         <v>43698</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>43699</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>43704</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>43704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>43704</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15774,7 +15774,7 @@
         <v>43704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15831,7 +15831,7 @@
         <v>43706</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>43707</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>43714</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>43717</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>43717</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>43719</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>43720</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>43720</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>43724</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>43724</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>43724</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>43727</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>43734</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>43734</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>43734</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>43735</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>43738</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>43739</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>43739</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>43739</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>43741</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>43742</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>43745</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>43748</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>43748</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>43751</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>43753</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>43755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17462,7 +17462,7 @@
         <v>43755</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>43755</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>43770</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>43776</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17690,7 +17690,7 @@
         <v>43776</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>43782</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>43782</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>43782</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17923,7 +17923,7 @@
         <v>43783</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>43783</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>43783</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>43787</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>43788</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>43788</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>43788</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18332,7 +18332,7 @@
         <v>43788</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>43795</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18446,7 +18446,7 @@
         <v>43801</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>43801</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>43801</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>43801</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>43802</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>43802</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>43802</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>43804</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>43805</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>43805</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>43805</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>43815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>43818</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>43820</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>43843</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>43844</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>43853</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>43859</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>43873</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>43885</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>43885</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>43885</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>43887</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>43888</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>43888</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>43889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>43909</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>43910</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>43913</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>43921</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>43921</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>43921</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>43922</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>43928</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>43928</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>43930</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>43941</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>43941</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>43942</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>43945</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>43950</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>43952</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43955</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43955</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>43955</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>43959</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>43961</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>43961</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>43963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>43963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>43963</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>43965</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>43965</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>43965</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>43966</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>43966</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>43966</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>43976</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>43978</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>43978</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>43980</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>43986</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>43986</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>43991</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>43993</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>43999</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>44000</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>44005</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44005</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>44005</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>44006</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44008</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>44008</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44011</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>44012</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>44012</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44013</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>44018</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>44019</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>44021</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44046</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44050</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23185,7 +23185,7 @@
         <v>44057</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>44057</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23299,7 +23299,7 @@
         <v>44062</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23356,7 +23356,7 @@
         <v>44068</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44069</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>44073</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>44074</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44078</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44083</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>44084</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44090</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44092</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44095</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>44095</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>44102</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44102</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>44104</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44105</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44105</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>44105</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>44106</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44109</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>44113</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44123</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44123</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44123</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>44124</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>44124</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24878,7 +24878,7 @@
         <v>44131</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>44132</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24997,7 +24997,7 @@
         <v>44133</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>44140</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25111,7 +25111,7 @@
         <v>44141</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>44143</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>44144</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>44146</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44146</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44146</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>44147</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44148</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>44151</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>44153</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>44155</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44158</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44158</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25862,7 +25862,7 @@
         <v>44158</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>44158</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44160</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>44160</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44162</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>44165</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44179</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44180</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>44182</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>44186</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>44186</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>44186</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>44186</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>44187</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26660,7 +26660,7 @@
         <v>44194</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>44214</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>44214</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>44214</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44214</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44217</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>44221</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>44222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44222</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44224</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27235,7 +27235,7 @@
         <v>44232</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44232</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44246</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>44249</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>44249</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>44249</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>44251</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>44257</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44274</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>44280</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44287</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>44293</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44294</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>44299</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>44305</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>44305</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>44306</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44308</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>44308</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44308</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>44309</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>44312</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44313</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>44314</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>44314</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>44320</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>44321</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>44322</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44326</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>44326</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28950,7 +28950,7 @@
         <v>44330</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>44333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>44341</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>44343</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>44350</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>44354</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>44354</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>44355</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>44355</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>44361</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>44361</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29577,7 +29577,7 @@
         <v>44376</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>44376</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29701,7 +29701,7 @@
         <v>44376</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>44378</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44379</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>44382</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>44382</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44382</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30053,7 +30053,7 @@
         <v>44385</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>44385</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30172,7 +30172,7 @@
         <v>44386</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44406</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>44406</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>44406</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44406</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>44406</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>44406</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30596,7 +30596,7 @@
         <v>44406</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>44406</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>44406</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>44406</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30839,7 +30839,7 @@
         <v>44406</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>44406</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>44406</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31020,7 +31020,7 @@
         <v>44406</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>44406</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31144,7 +31144,7 @@
         <v>44406</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         <v>44406</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>44407</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>44407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31392,7 +31392,7 @@
         <v>44407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>44407</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31506,7 +31506,7 @@
         <v>44407</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>44407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>44407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>44407</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31754,7 +31754,7 @@
         <v>44407</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31816,7 +31816,7 @@
         <v>44407</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>44407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>44407</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>44407</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>44407</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>44407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32302,7 +32302,7 @@
         <v>44407</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32364,7 +32364,7 @@
         <v>44407</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44407</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32488,7 +32488,7 @@
         <v>44407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>44407</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
         <v>44407</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32674,7 +32674,7 @@
         <v>44410</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32736,7 +32736,7 @@
         <v>44410</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>44410</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>44410</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44410</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44410</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33046,7 +33046,7 @@
         <v>44410</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>44410</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44410</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44410</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44410</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
         <v>44410</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45270</v>
+        <v>45271</v>
       </c>
       <c r="D516" t="inlineStr">
 